--- a/spravki/spravka_rnntd_region_2026-09-30.xlsx
+++ b/spravki/spravka_rnntd_region_2026-09-30.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -512,16 +512,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -531,11 +531,11 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>705</v>
+        <v>754</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -564,77 +564,77 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>394</v>
+        <v>416</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Астана</t>
+          <t>Не указано</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>229</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Не указано</t>
+          <t>Астана</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>91</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10">
@@ -644,16 +644,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -667,26 +667,26 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Карагандинская область</t>
+          <t>Туркестанская область</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -696,30 +696,30 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>137</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Туркестанская область</t>
+          <t>Карагандинская область</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -743,11 +743,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -776,16 +776,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -795,30 +795,30 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ВКО</t>
+          <t>Шымкент</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -828,11 +828,11 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>98</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16">
@@ -842,16 +842,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -865,26 +865,26 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Шымкент</t>
+          <t>ВКО</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -894,50 +894,50 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>58</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ЗКО</t>
+          <t>Павлодарская область</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>37</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Павлодарская область</t>
+          <t>ЗКО</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -945,7 +945,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -955,16 +955,16 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
       <c r="G19" t="n">
-        <v>71</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -1069,15 +1069,15 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Костанайская область</t>
+          <t>Жетисуская область</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1096,13 +1096,13 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Жетисуская область</t>
+          <t>Костанайская область</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1129,13 +1129,46 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Источник: «Показатели проектов на 30.09.2026», проектов в выборке — 407. Сформировано 16.10.2026.</t>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Источник: «Показатели проектов на 30.09.2026», проектов в выборке — 475. Сформировано 16.10.2026.</t>
         </is>
       </c>
     </row>
